--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92109</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>136968550</v>
       </c>
       <c r="B22" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136969634</v>
       </c>
       <c r="B23" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136968548</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>136968549</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136968552</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136968556</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>136968560</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>136968562</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136968563</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>136968564</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>136968565</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>136969625</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136969627</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>136969628</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>136968541</v>
       </c>
       <c r="B36" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>136968544</v>
       </c>
       <c r="B37" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>136968559</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>136969630</v>
       </c>
       <c r="B39" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>136968555</v>
       </c>
       <c r="B40" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>136968550</v>
       </c>
       <c r="B22" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136969634</v>
       </c>
       <c r="B23" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136968548</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>136968549</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>136968552</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>136968556</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>136968560</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>136968562</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136968563</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>136968564</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>136968565</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>136969625</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         <v>136969627</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>136969628</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>136968541</v>
       </c>
       <c r="B36" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>136968544</v>
       </c>
       <c r="B37" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>136968559</v>
       </c>
       <c r="B38" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>136969630</v>
       </c>
       <c r="B39" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>136968555</v>
       </c>
       <c r="B40" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -3024,11 +3024,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -3141,11 +3137,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Paljackaberget, Dlr</t>
@@ -3258,11 +3250,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -3375,11 +3363,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -3492,11 +3476,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -3613,11 +3593,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -3730,11 +3706,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -3847,11 +3819,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -3964,11 +3932,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -4081,11 +4045,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -4198,11 +4158,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -4315,11 +4271,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paljackaberget, Dlr</t>
@@ -4432,11 +4384,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paljackaberget, Dlr</t>
@@ -4549,11 +4497,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paljackaberget, Dlr</t>
@@ -4778,11 +4722,7 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -4895,11 +4835,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Paljackberget, Dlr</t>
@@ -5012,11 +4948,7 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Paljackaberget, Dlr</t>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>136968550</v>
       </c>
       <c r="B22" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136969634</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136968548</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>136968549</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136968552</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>136968556</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>136968560</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136968562</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>136968563</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>136968564</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>136968565</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136969625</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136969627</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136969628</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>136968541</v>
       </c>
       <c r="B36" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>136968544</v>
       </c>
       <c r="B37" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>136968559</v>
       </c>
       <c r="B38" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136969630</v>
       </c>
       <c r="B39" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>136968555</v>
       </c>
       <c r="B40" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>136968550</v>
       </c>
       <c r="B22" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136969634</v>
       </c>
       <c r="B23" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136968548</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>136968549</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136968552</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>136968556</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>136968560</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136968562</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>136968563</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>136968564</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>136968565</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136969625</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136969627</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136969628</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>136968541</v>
       </c>
       <c r="B36" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>136968544</v>
       </c>
       <c r="B37" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>136968559</v>
       </c>
       <c r="B38" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136969630</v>
       </c>
       <c r="B39" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>136968555</v>
       </c>
       <c r="B40" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>136968550</v>
       </c>
       <c r="B22" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136969634</v>
       </c>
       <c r="B23" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136968548</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>136968549</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136968552</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>136968556</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>136968560</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136968562</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>136968563</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>136968564</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>136968565</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136969625</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136969627</v>
       </c>
       <c r="B34" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136969628</v>
       </c>
       <c r="B35" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>136968541</v>
       </c>
       <c r="B36" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>136968544</v>
       </c>
       <c r="B37" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>136968559</v>
       </c>
       <c r="B38" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136969630</v>
       </c>
       <c r="B39" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>136968555</v>
       </c>
       <c r="B40" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89543</v>
+        <v>89544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80655</v>
+        <v>80656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2026 artfynd.xlsx
+++ b/artfynd/A 35041-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136968557</v>
       </c>
       <c r="B2" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136968558</v>
       </c>
       <c r="B3" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136968545</v>
       </c>
       <c r="B4" t="n">
-        <v>89544</v>
+        <v>89547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136968554</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136968569</v>
       </c>
       <c r="B6" t="n">
-        <v>80652</v>
+        <v>80655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136968539</v>
       </c>
       <c r="B7" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136968540</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136968543</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136968547</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136968566</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136968575</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136969626</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>136969629</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>136969632</v>
       </c>
       <c r="B15" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>136969635</v>
       </c>
       <c r="B16" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136968568</v>
       </c>
       <c r="B17" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136968571</v>
       </c>
       <c r="B18" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>136968573</v>
       </c>
       <c r="B19" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>136969636</v>
       </c>
       <c r="B20" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>136968572</v>
       </c>
       <c r="B21" t="n">
-        <v>80656</v>
+        <v>80659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>136968550</v>
       </c>
       <c r="B22" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>136969634</v>
       </c>
       <c r="B23" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>136968548</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>136968549</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>136968552</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>136968556</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>136968560</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>136968562</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>136968563</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>136968564</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>136968565</v>
       </c>
       <c r="B32" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>136969625</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136969627</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>136969628</v>
       </c>
       <c r="B35" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>136968541</v>
       </c>
       <c r="B36" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>136968544</v>
       </c>
       <c r="B37" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>136968559</v>
       </c>
       <c r="B38" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         <v>136969630</v>
       </c>
       <c r="B39" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>136968555</v>
       </c>
       <c r="B40" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
